--- a/인물퀴즈_MC진행용_정답표_v2.xlsx
+++ b/인물퀴즈_MC진행용_정답표_v2.xlsx
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B9" s="33" t="inlineStr">
         <is>
-          <t>잔망루피</t>
+          <t>트랄랄레로 트랄랄라</t>
         </is>
       </c>
       <c r="C9" s="33" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="N13" s="33" t="inlineStr">
         <is>
-          <t>김하성</t>
+          <t>김창섭(신창섭)</t>
         </is>
       </c>
       <c r="O13" s="33" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="P13" s="33" t="inlineStr">
         <is>
-          <t>허훈</t>
+          <t>금강선(로스트아크 디렉터)</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K18" s="30" t="inlineStr">
         <is>
-          <t>백종원 (PAIK JONG WON)</t>
+          <t>승우아빠</t>
         </is>
       </c>
       <c r="L18" s="30" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="K19" s="33" t="inlineStr">
         <is>
-          <t>너덜트</t>
+          <t>도파</t>
         </is>
       </c>
       <c r="L19" s="33" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="C20" s="27" t="inlineStr">
         <is>
-          <t>핑구</t>
+          <t>퉁*9 사후르 (퉁퉁퉁퉁퉁퉁퉁퉁퉁 사후르)</t>
         </is>
       </c>
       <c r="D20" s="27" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="O25" s="33" t="inlineStr">
         <is>
-          <t>정의선</t>
+          <t>박나은 프로님</t>
         </is>
       </c>
       <c r="P25" s="33" t="inlineStr">
         <is>
-          <t>구본길</t>
+          <t>김준호 강사님</t>
         </is>
       </c>
     </row>
@@ -2986,17 +2986,17 @@
       </c>
       <c r="F5" s="42" t="inlineStr">
         <is>
-          <t>잔망루피</t>
+          <t>트랄랄레로 트랄랄라</t>
         </is>
       </c>
       <c r="G5" s="43" t="inlineStr">
         <is>
-          <t>카카오톡 이모티콘 1위, 2030 직장인 흑화/해탈 밈의 상징</t>
+          <t>나이키 신발을 신은 세 발 달린 상어, 이탈리안 브레인롯 밈 (Tralalero Tralala)</t>
         </is>
       </c>
       <c r="H5" s="44" t="inlineStr">
         <is>
-          <t>images/애니_1단계/잔망루피.jpg</t>
+          <t>images/애니_1단계/트랄랄레로 트랄랄라.jpg</t>
         </is>
       </c>
     </row>
@@ -4226,17 +4226,17 @@
       </c>
       <c r="F36" s="37" t="inlineStr">
         <is>
-          <t>핑구</t>
+          <t>퉁*9 사후르 (퉁퉁퉁퉁퉁퉁퉁퉁퉁 사후르)</t>
         </is>
       </c>
       <c r="G36" s="38" t="inlineStr">
         <is>
-          <t>'눱눱!', 점토 클레이 애니메이션의 전설, 2030 추억의 짤</t>
+          <t>야구 방망이를 든 통나무 괴물, 퉁을 9번 외치는 이탈리안 브레인롯 밈 (Tung Tung... Sahur)</t>
         </is>
       </c>
       <c r="H36" s="39" t="inlineStr">
         <is>
-          <t>images/애니_2단계/핑구.jpg</t>
+          <t>images/애니_2단계/퉁퉁퉁퉁퉁퉁퉁퉁퉁 사후르.jpg</t>
         </is>
       </c>
     </row>
@@ -10546,17 +10546,17 @@
       </c>
       <c r="F194" s="37" t="inlineStr">
         <is>
-          <t>백종원 (PAIK JONG WON)</t>
+          <t>승우아빠</t>
         </is>
       </c>
       <c r="G194" s="38" t="inlineStr">
         <is>
-          <t>자취생 초간단 레시피, 외식업 솔루션, 2030 요리 초보들의 구세주</t>
+          <t>에드워드 권 사단 셰프 출신 요리 크리에이터 (목진화), '세상의 모든 요리'</t>
         </is>
       </c>
       <c r="H194" s="39" t="inlineStr">
         <is>
-          <t>images/유튜버_1단계/백종원 (PAIK JONG WON).jpg</t>
+          <t>images/유튜버_1단계/승우아빠.jpg</t>
         </is>
       </c>
     </row>
@@ -10586,17 +10586,17 @@
       </c>
       <c r="F195" s="42" t="inlineStr">
         <is>
-          <t>너덜트</t>
+          <t>도파</t>
         </is>
       </c>
       <c r="G195" s="43" t="inlineStr">
         <is>
-          <t>당근마켓 짤, 일상 속 웃픈 순간을 감각적인 편집으로 담아낸 코미디</t>
+          <t>LoL 천상계 미드 라이너이자 인터넷 방송인 (정상길), '압도', '도파'</t>
         </is>
       </c>
       <c r="H195" s="44" t="inlineStr">
         <is>
-          <t>images/유튜버_1단계/너덜트.jpg</t>
+          <t>images/유튜버_1단계/도파.jpg</t>
         </is>
       </c>
     </row>
@@ -12746,17 +12746,17 @@
       </c>
       <c r="F249" s="42" t="inlineStr">
         <is>
-          <t>김하성</t>
+          <t>김창섭(신창섭)</t>
         </is>
       </c>
       <c r="G249" s="43" t="inlineStr">
         <is>
-          <t>MLB 골드글러브 수상, 몸을 아끼지 않는 허슬 플레이로 2030 팬덤 확보</t>
+          <t>넥슨 메이플스토리 총괄 디렉터, '다 해줬잖아', '정상화' 밈의 주인공</t>
         </is>
       </c>
       <c r="H249" s="44" t="inlineStr">
         <is>
-          <t>images/종합_1단계/김하성.jpg</t>
+          <t>images/종합_1단계/김창섭(신창섭).jpg</t>
         </is>
       </c>
     </row>
@@ -14026,17 +14026,17 @@
       </c>
       <c r="F281" s="42" t="inlineStr">
         <is>
-          <t>정의선</t>
+          <t>박나은 프로님</t>
         </is>
       </c>
       <c r="G281" s="43" t="inlineStr">
         <is>
-          <t>아이오닉·EV 시리즈 전기차 혁신, 2030 직장인 취업 선호도 1위</t>
+          <t>우리의 든든한 SSAFY 운영 프로님</t>
         </is>
       </c>
       <c r="H281" s="44" t="inlineStr">
         <is>
-          <t>images/종합_2단계/정의선.jpg</t>
+          <t>images/종합_2단계/박나은 프로님.jpg</t>
         </is>
       </c>
     </row>
@@ -14346,17 +14346,17 @@
       </c>
       <c r="F289" s="42" t="inlineStr">
         <is>
-          <t>허훈</t>
+          <t>금강선(로스트아크 디렉터)</t>
         </is>
       </c>
       <c r="G289" s="43" t="inlineStr">
         <is>
-          <t>농구 대통령 허재의 아들, 화려한 드리블과 득점력의 가드 스타</t>
+          <t>스마일게이트 RPG CCO, '빛강선', '로아온'의 전설적인 로스트아크 총괄 디렉터</t>
         </is>
       </c>
       <c r="H289" s="44" t="inlineStr">
         <is>
-          <t>images/종합_3단계/허훈.jpg</t>
+          <t>images/종합_3단계/금강선(로스트아크 디렉터).jpg</t>
         </is>
       </c>
     </row>
@@ -14826,17 +14826,17 @@
       </c>
       <c r="F301" s="42" t="inlineStr">
         <is>
-          <t>구본길</t>
+          <t>김준호 강사님</t>
         </is>
       </c>
       <c r="G301" s="43" t="inlineStr">
         <is>
-          <t>어펜져스 맏형, 화려한 검술과 파이팅 넘치는 펜싱 스타</t>
+          <t>열정과 실력을 겸비한 SSAFY 담당 강사님</t>
         </is>
       </c>
       <c r="H301" s="44" t="inlineStr">
         <is>
-          <t>images/종합_3단계/구본길.jpg</t>
+          <t>images/종합_3단계/김준호 강사님.jpg</t>
         </is>
       </c>
     </row>
@@ -15095,12 +15095,12 @@
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>잔망루피</t>
+          <t>트랄랄레로 트랄랄라</t>
         </is>
       </c>
       <c r="C7" s="52" t="inlineStr">
         <is>
-          <t>카카오톡 이모티콘 1위, 2030 직장인 흑화/해탈 밈의 상징</t>
+          <t>나이키 신발을 신은 세 발 달린 상어, 이탈리안 브레인롯 밈 (Tralalero Tralala)</t>
         </is>
       </c>
       <c r="E7" s="51" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="F18" s="27" t="inlineStr">
         <is>
-          <t>핑구</t>
+          <t>퉁*9 사후르 (퉁퉁퉁퉁퉁퉁퉁퉁퉁 사후르)</t>
         </is>
       </c>
       <c r="G18" s="50" t="inlineStr">
         <is>
-          <t>'눱눱!', 점토 클레이 애니메이션의 전설, 2030 추억의 짤</t>
+          <t>야구 방망이를 든 통나무 괴물, 퉁을 9번 외치는 이탈리안 브레인롯 밈 (Tung Tung... Sahur)</t>
         </is>
       </c>
       <c r="I18" s="49" t="inlineStr">
@@ -18671,12 +18671,12 @@
       </c>
       <c r="B16" s="30" t="inlineStr">
         <is>
-          <t>백종원 (PAIK JONG WON)</t>
+          <t>승우아빠</t>
         </is>
       </c>
       <c r="C16" s="70" t="inlineStr">
         <is>
-          <t>자취생 초간단 레시피, 외식업 솔루션, 2030 요리 초보들의 구세주</t>
+          <t>에드워드 권 사단 셰프 출신 요리 크리에이터 (목진화), '세상의 모든 요리'</t>
         </is>
       </c>
       <c r="E16" s="69" t="inlineStr">
@@ -18718,12 +18718,12 @@
       </c>
       <c r="B17" s="33" t="inlineStr">
         <is>
-          <t>너덜트</t>
+          <t>도파</t>
         </is>
       </c>
       <c r="C17" s="52" t="inlineStr">
         <is>
-          <t>당근마켓 짤, 일상 속 웃픈 순간을 감각적인 편집으로 담아낸 코미디</t>
+          <t>LoL 천상계 미드 라이너이자 인터넷 방송인 (정상길), '압도', '도파'</t>
         </is>
       </c>
       <c r="E17" s="51" t="inlineStr">
@@ -19487,12 +19487,12 @@
       </c>
       <c r="B11" s="33" t="inlineStr">
         <is>
-          <t>김하성</t>
+          <t>김창섭(신창섭)</t>
         </is>
       </c>
       <c r="C11" s="52" t="inlineStr">
         <is>
-          <t>MLB 골드글러브 수상, 몸을 아끼지 않는 허슬 플레이로 2030 팬덤 확보</t>
+          <t>넥슨 메이플스토리 총괄 디렉터, '다 해줬잖아', '정상화' 밈의 주인공</t>
         </is>
       </c>
       <c r="E11" s="51" t="inlineStr">
@@ -19517,12 +19517,12 @@
       </c>
       <c r="J11" s="33" t="inlineStr">
         <is>
-          <t>허훈</t>
+          <t>금강선(로스트아크 디렉터)</t>
         </is>
       </c>
       <c r="K11" s="52" t="inlineStr">
         <is>
-          <t>농구 대통령 허재의 아들, 화려한 드리블과 득점력의 가드 스타</t>
+          <t>스마일게이트 RPG CCO, '빛강선', '로아온'의 전설적인 로스트아크 총괄 디렉터</t>
         </is>
       </c>
     </row>
@@ -20066,12 +20066,12 @@
       </c>
       <c r="F23" s="33" t="inlineStr">
         <is>
-          <t>정의선</t>
+          <t>박나은 프로님</t>
         </is>
       </c>
       <c r="G23" s="52" t="inlineStr">
         <is>
-          <t>아이오닉·EV 시리즈 전기차 혁신, 2030 직장인 취업 선호도 1위</t>
+          <t>우리의 든든한 SSAFY 운영 프로님</t>
         </is>
       </c>
       <c r="I23" s="51" t="inlineStr">
@@ -20081,12 +20081,12 @@
       </c>
       <c r="J23" s="33" t="inlineStr">
         <is>
-          <t>구본길</t>
+          <t>김준호 강사님</t>
         </is>
       </c>
       <c r="K23" s="52" t="inlineStr">
         <is>
-          <t>어펜져스 맏형, 화려한 검술과 파이팅 넘치는 펜싱 스타</t>
+          <t>열정과 실력을 겸비한 SSAFY 담당 강사님</t>
         </is>
       </c>
     </row>
